--- a/datasets/lgbtq_eurovision_artists.xlsx
+++ b/datasets/lgbtq_eurovision_artists.xlsx
@@ -5086,7 +5086,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bisexual [b][104]</t>
+          <t>Bisexual[b][104]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
